--- a/Result/profitability/5251.xlsx
+++ b/Result/profitability/5251.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM62"/>
+  <dimension ref="A1:AM63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8304,6 +8304,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>96</v>
+      </c>
+      <c r="D63" t="n">
+        <v>55</v>
+      </c>
+      <c r="E63" t="n">
+        <v>41</v>
+      </c>
+      <c r="F63" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>4.01%</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>19</v>
+      </c>
+      <c r="J63" t="n">
+        <v>23</v>
+      </c>
+      <c r="K63" t="n">
+        <v>23</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.08375</v>
+      </c>
+      <c r="N63" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="X63" t="n">
+        <v>5.899999999999999</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-0.2600000000000051</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-0.006008782066096674</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>-2.682926829268292</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.809999999999995</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.06990049751243776</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK63" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
